--- a/analysis/tables/mood_power_comparison.xlsx
+++ b/analysis/tables/mood_power_comparison.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve">Сценарий</t>
   </si>
@@ -27,6 +27,15 @@
   </si>
   <si>
     <t xml:space="preserve">% значим (истинный)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сред. p (наш, M̂)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сред. p (истинный)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дельта mean(p)</t>
   </si>
   <si>
     <t xml:space="preserve">Согласие решений, %</t>
@@ -174,8 +183,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -211,9 +221,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,12 +518,15 @@
     <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="32.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="18.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="13.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="12.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,573 +557,756 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>1000</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E2" s="1" t="n">
+      <c r="D2" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
+        <v>0.516548072443228</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>0.565124944037518</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0.0485768715942902</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>97.6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>1000</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="D3" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>3.4</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="n">
-        <v>61</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
+        <v>0.589007925407925</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.597283916083916</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.00827599067599072</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>57</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>1000</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="E4" s="1" t="n">
+      <c r="D4" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>14.1</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>74.1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>256</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
+        <v>0.460261202406735</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.492172864368217</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0.0319116619614813</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="D5" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="n">
-        <v>108</v>
-      </c>
-      <c r="I5" t="n">
-        <v>25</v>
+        <v>0.350639175753344</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.385295814008582</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.034656638255238</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>94.6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>53</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="E6" s="1" t="n">
+      <c r="D6" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>89.6</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>103</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
+        <v>0.4756</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.588114285714286</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.112514285714286</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>89.4</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>106</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>1000</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="D7" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>99.9</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>99.9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="n">
+        <v>0.000840870623226771</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.000874063837492298</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.0000331932142655266</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>99.6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
+      <c r="L7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="E8" s="1" t="n">
+      <c r="D8" s="2" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>56.6</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>53</v>
-      </c>
-      <c r="I8" t="n">
-        <v>47</v>
+        <v>0.138066296405385</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.155101180874241</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.0170348844688558</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
         <v>1000</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="D9" s="2" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>33.3</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" t="n">
-        <v>81</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
+        <v>0.227891752268853</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.246837164761938</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.0189454124930851</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>91.9</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>1000</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="E10" s="1" t="n">
+      <c r="D10" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>98.2</v>
       </c>
       <c r="F10" s="1" t="n">
+        <v>0.00227171822721366</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.00304862820767018</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.00077690998045652</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>98.4</v>
       </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" t="n">
-        <v>12</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>13</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>87.6</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.025536853058863</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0.0282256628382984</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0.00268880977943538</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>14</v>
+      </c>
+      <c r="L11" t="n">
         <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>88.9</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>95.9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>1000</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>0.999646288537111</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.998586017385691</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>-0.00106027115141916</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="J12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
         <v>1000</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="D13" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>3.3</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>0.573734741177576</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.605334219982752</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.0315994788051758</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>97.7</v>
       </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" t="n">
-        <v>19</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" t="n">
+        <v>18</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
         <v>1000</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="E14" s="1" t="n">
+      <c r="D14" s="2" t="n">
+        <v>98.9</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>98.6</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
+        <v>0.00237797463517855</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.00246639310277094</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0.0000884184675923856</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C15" t="n">
         <v>1000</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="E15" s="1" t="n">
+      <c r="D15" s="2" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>32</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" t="n">
-        <v>159</v>
-      </c>
-      <c r="I15" t="n">
-        <v>18</v>
+        <v>0.194935801780666</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.223897402368798</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0.0289616005881317</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" t="n">
+        <v>132</v>
+      </c>
+      <c r="L15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="1"/>
-      <c r="G16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16"/>
-      <c r="I16"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="2"/>
+      <c r="J16" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C17" t="n">
         <v>1000</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.6328</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0.0632999999999999</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G17" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="J17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C18" t="n">
         <v>1000</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>34.9</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>34.9</v>
-      </c>
       <c r="F18" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" t="n">
-        <v>50</v>
-      </c>
-      <c r="I18" t="n">
-        <v>50</v>
+        <v>0.245085165584988</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.264636766609608</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0.0195516010246199</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24</v>
+      </c>
+      <c r="L18" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C19" t="n">
         <v>1000</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="2" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0.00685952322254376</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>0.00942920643871473</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>0.00256968321617098</v>
+      </c>
+      <c r="I19" s="2" t="n">
         <v>97.2</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="G19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" t="n">
-        <v>22</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" t="n">
+        <v>25</v>
+      </c>
+      <c r="L19" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" t="n">
         <v>1000</v>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="E20" s="1" t="n">
+      <c r="D20" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>87.4</v>
-      </c>
-      <c r="G20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" t="n">
-        <v>125</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
+        <v>0.54245180734223</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>0.606651230592217</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>0.0641994232499866</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" t="n">
+        <v>32</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C21" t="n">
         <v>1000</v>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="E21" s="1" t="n">
+      <c r="D21" s="2" t="n">
+        <v>86.6</v>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>82.6</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" t="n">
-        <v>56</v>
-      </c>
-      <c r="I21" t="n">
-        <v>12</v>
+        <v>0.0324219246427649</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>0.0358136377267713</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>0.00339171308400638</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="J21" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" t="n">
+        <v>49</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
